--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,310 +444,53 @@
           <t>Precio</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Enlace</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Memory Kings</t>
+          <t>⭐ Impacto</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LAPTOP Core i5-12450HX LENOVO LOQ 15IAX9 Gaming 8|512|15.6" GEFORCE RTX 3050 6GB</t>
+          <t>[52% Match] MK: LAPTOP Core Ultra 7 255H LENOVO ThinkBook 16 G8 IAL 16|... │ IMP: LAPTOP DELL PRO CORE ULTRA 7-150U PC16250 (40VPG) 16 GH...</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S/ 3129.00</t>
+          <t>MK: S/ 5037.00 │ IMP: S/ 3918.16 (Ahorras S/ 1118.84)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.impacto.com.pe/producto/laptop-dell-pro-core-ultra-7-150u-pc16250-40vpg-pantalla-16-ram-16gb-ssd-512gb-win11-pronegro-22148</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Memory Kings</t>
+          <t>⭐ Impacto</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LAPTOP Core i5-13420H LENOVO IdeaPad Slim3 15IRH10 8|512|15.3" grafica Intel UHD</t>
+          <t>[59% Match] MK: LAPTOP Core Ultra 7 155H HP ZBook Power 16 G11 16|S1TB|... │ IMP: LAPTOP LENOVO CORE ULTRA 7 155H THINKPAD P16V GEN 2 (21...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S/ 2104.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Memory Kings</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LAPTOP Core i5-13420H LENOVO IdeaPad Slim3 16IRH10 16|512|16" grafica Intel UHD</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>S/ 2535.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Memory Kings</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LAPTOP Core i5-13420H LENOVO V15 G5 IRL 16|512 16|512|15.6" grafica Intel UHD</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>S/ 2449.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Memory Kings</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LAPTOP Core i5-13420H MSI Cyborg 15 A13VE 16|512|15.6" GEFORCE RTX 4050 6GB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>S/ 4450.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Memory Kings</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LAPTOP Core i5-13450HX ASUS TUF Gaming F16 FX608JH-RV010 16|512|16" GEFORCE RTX 5050 8GB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>S/ 4778.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LAPTOP ASUS CORE I5 210H EXPERTBOOK P1 P1503CVA-S72381 (90NX0881-M02P90) RAM 16GB DDR5, SSD 512GB, PANTALLA 15.6" FHD IPS, FREEDOS, MISTY GREY</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>S/ 2683.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LAPTOP HP CORE I5-13420H VICTUS 15-FA2035LA (D74JMLA#ABM) RAM 8GB, SSD 512GB, RTX 3050 6GB, 15.6 FHD 144HZ IPS, FREEDOS, IRON GREY, ESP</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>S/ 3176.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LAPTOP HAIER CORE I5-1135G7 Y15T (RP-HAIER) RAM 8GB, SSD 256GB, PANTALLA 15.6 FHD, FREEDOS, PLATA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>S/ 1386.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LAPTOP ASUS CORE I5 120U VIVOBOOK 14 X1404VAP (90NB13U1-M00K70) PANTALLA 14 FHD, RAM 8GB, SSD 256GB, WIN11 HOME, QUIET BLUE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>S/ 1990.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LAPTOP DELL CORE I5-1334U 15 DC15250 M4CFY (LDC15250-5434BLK-PUS) RAM 8GB, SSD 512GB, PANTALLA 15.6 FHD TACTIL IPS, WIN11 HOME, CARBON BLACK</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>S/ 2409.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LAPTOP LENOVO CORE I5-13450HX LOQ 15IRX11 GAMING (83SC0055LM) 15.6 FHD, RAM 16GB, SSD 512GB, RTX 5050 8GB, S/S, 13GEN.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>S/ 4110.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LAPTOP HP CORE I5-1334U 250 G10 (B5UU9AT) PANTALLA 15.6 HD, RAM 8GB, SSD 512GB, S/SISTEMA, PLATEADO CENIZA OSCURO</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>S/ 1978.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LAPTOP HP CORE I5-1334U 15-FD0152LA (B9TS2LAABM) PANTALLA 15.6 FHD IPS TACTIL, RAM 8GB, SSD 512GB, S/S, DORADO CON PLATA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>S/ 2184.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LAPTOP LENOVO CORE I5-13420H V15 G5 IRL (83GW005LLD) PANTALLA 15.6 FHD, RAM 8GB, SSD 512GB, FREEDOS, IRON GREY, ESP</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>S/ 2046.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LAPTOP LENOVO CORE I5-12450HX LOQ 15IAX9 GAMING (83GS006WLM) 15.6 FHD 144HZ, RAM 8GB, SSD 512GB, NVIDIA RTX 3050 6GB NVIDIA, S/S, 12 GEN.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>S/ 3010.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LAPTOP LENOVO CORE I5-13420H IDEAPAD SLIM 3 15IRH10 (83K10152LM) PANTALLA 15.3 TACTIL , RAM 8GB, SSD 512GB, FREEDOS TOUCH</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>S/ 2132.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Impacto</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LAPTOP HAIER CORE I5-1135G7 Y15T I5 (1LGF0000326) RAM 8GB, SSD 512GB, PANTALLA 15.6 FHD, FREEDOS, PLATA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>S/ 1491.24</t>
+          <t>MK: S/ 9401.00 │ IMP: S/ 8393.60 (Ahorras S/ 1007.40)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.impacto.com.pe/producto/laptop-lenovo-core-ultra-7-155h-thinkpad-p16v-gen-2-21ky000nlm-pantalla-16-wuxga-ram-32gb-ssd-1tb-rtx-1000-ada-6gb-win11-pro-negro</t>
         </is>
       </c>
     </row>
